--- a/InputData/ccs/CCP/CO2 Capture Potentials.xlsx
+++ b/InputData/ccs/CCP/CO2 Capture Potentials.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="23628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CodeRepositories\eps-us\InputData\ccs\CCP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndonesiaEPS/Shared Documents/Updated Indonesia InputData files/ccs/CCP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6134759D-C76E-400C-8C70-93E8AFC83C7B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{6134759D-C76E-400C-8C70-93E8AFC83C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57545826-3D0C-47DB-A7BC-66C9E9A2E986}"/>
   <bookViews>
-    <workbookView xWindow="21045" yWindow="1410" windowWidth="33360" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="1080" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="CPPbES" sheetId="12" r:id="rId2"/>
     <sheet name="CPPbI" sheetId="13" r:id="rId3"/>
+    <sheet name="CPPbHS" sheetId="14" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
   <si>
     <t>Source:</t>
   </si>
@@ -50,9 +51,6 @@
   </si>
   <si>
     <t>hard coal</t>
-  </si>
-  <si>
-    <t>natural gas nonpeaker</t>
   </si>
   <si>
     <t>nuclear</t>
@@ -290,6 +288,39 @@
   <si>
     <t>(We assume CO2 from "water and waste" is from waste collection trucks, not water treatment plants, which use almost entirely electricity.)</t>
   </si>
+  <si>
+    <t>capture rate</t>
+  </si>
+  <si>
+    <t>natural gas reforming with CCS</t>
+  </si>
+  <si>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
+  </si>
+  <si>
+    <t>hard coal w CCS</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle w CCS</t>
+  </si>
+  <si>
+    <t>biomass w CCS</t>
+  </si>
+  <si>
+    <t>lignite w CCS</t>
+  </si>
+  <si>
+    <t>small modular reactor</t>
+  </si>
+  <si>
+    <t>hydrogen combustion turbine</t>
+  </si>
+  <si>
+    <t>hydrogen combined cycle</t>
+  </si>
 </sst>
 </file>
 
@@ -298,7 +329,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -331,6 +362,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -358,18 +396,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -393,9 +430,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -433,9 +470,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -468,26 +505,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -520,26 +540,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -736,12 +739,9 @@
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="7"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
@@ -749,97 +749,88 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>22</v>
+      <c r="A10" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="1"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="1"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="7"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+      <c r="B22" s="6"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="10"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
+      <c r="B23" s="6"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -853,15 +844,15 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>21</v>
+      <c r="A1" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -869,20 +860,20 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -890,7 +881,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -898,7 +889,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -906,7 +897,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -914,7 +905,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -922,15 +913,15 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -938,31 +929,31 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -970,26 +961,90 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1012,19 +1067,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>21</v>
+      <c r="A1" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="B1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" t="s">
         <v>33</v>
-      </c>
-      <c r="C1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1035,7 +1090,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1046,7 +1101,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1057,7 +1112,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1068,7 +1123,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1079,7 +1134,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1090,7 +1145,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1101,7 +1156,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1112,7 +1167,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1123,7 +1178,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -1134,7 +1189,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -1145,7 +1200,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1156,7 +1211,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -1167,7 +1222,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -1178,7 +1233,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -1189,7 +1244,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1200,7 +1255,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -1211,7 +1266,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -1222,7 +1277,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -1233,7 +1288,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -1244,7 +1299,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -1255,7 +1310,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -1266,7 +1321,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -1277,7 +1332,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -1288,7 +1343,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1300,4 +1355,232 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{951FAFB8-BAE4-4614-9A6D-88D6B842867F}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="45.42578125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2">
+        <v>0.85</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
+    <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1659011e-6b88-4225-9a61-aaf33aaf19e8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8776419D-BB7A-4C56-A5C2-D0CE5407A109}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{619070C5-9202-47DF-8813-ED214BB1F863}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BBC59DC-515F-4D18-937C-22F6B7DDAA6A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>